--- a/Data/MST/Fields.xlsx
+++ b/Data/MST/Fields.xlsx
@@ -32114,7 +32114,9 @@
       <c r="F1212" t="n">
         <v>19846</v>
       </c>
-      <c r="G1212" t="inlineStr"/>
+      <c r="G1212" t="n">
+        <v>297.0297029703029</v>
+      </c>
     </row>
     <row r="1213">
       <c r="A1213" t="n">
@@ -32140,7 +32142,7 @@
         <v>17606</v>
       </c>
       <c r="G1213" t="n">
-        <v>397.350993377494</v>
+        <v>50.04170141784829</v>
       </c>
     </row>
     <row r="1214">
@@ -32166,7 +32168,9 @@
       <c r="F1214" t="n">
         <v>18103</v>
       </c>
-      <c r="G1214" t="inlineStr"/>
+      <c r="G1214" t="n">
+        <v>67.49156355455553</v>
+      </c>
     </row>
     <row r="1215">
       <c r="A1215" t="n">
@@ -32191,7 +32195,9 @@
       <c r="F1215" t="n">
         <v>24956</v>
       </c>
-      <c r="G1215" t="inlineStr"/>
+      <c r="G1215" t="n">
+        <v>259.7402597402597</v>
+      </c>
     </row>
     <row r="1216">
       <c r="A1216" t="n">
@@ -32216,7 +32222,9 @@
       <c r="F1216" t="n">
         <v>29197</v>
       </c>
-      <c r="G1216" t="inlineStr"/>
+      <c r="G1216" t="n">
+        <v>61.6016427104724</v>
+      </c>
     </row>
     <row r="1217">
       <c r="A1217" t="n">
@@ -32241,7 +32249,9 @@
       <c r="F1217" t="n">
         <v>32152</v>
       </c>
-      <c r="G1217" t="inlineStr"/>
+      <c r="G1217" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="1218">
       <c r="A1218" t="n">
@@ -32266,7 +32276,9 @@
       <c r="F1218" t="n">
         <v>20766</v>
       </c>
-      <c r="G1218" t="inlineStr"/>
+      <c r="G1218" t="n">
+        <v>170.9401709401709</v>
+      </c>
     </row>
     <row r="1219">
       <c r="A1219" t="n">
@@ -32291,7 +32303,9 @@
       <c r="F1219" t="n">
         <v>12909</v>
       </c>
-      <c r="G1219" t="inlineStr"/>
+      <c r="G1219" t="n">
+        <v>1034.482758620761</v>
+      </c>
     </row>
     <row r="1220">
       <c r="A1220" t="n">
@@ -32316,7 +32330,9 @@
       <c r="F1220" t="n">
         <v>21412</v>
       </c>
-      <c r="G1220" t="inlineStr"/>
+      <c r="G1220" t="n">
+        <v>2400.000000000384</v>
+      </c>
     </row>
     <row r="1221">
       <c r="A1221" t="n">
@@ -32341,7 +32357,9 @@
       <c r="F1221" t="n">
         <v>27819</v>
       </c>
-      <c r="G1221" t="inlineStr"/>
+      <c r="G1221" t="n">
+        <v>81.19079837618382</v>
+      </c>
     </row>
     <row r="1222">
       <c r="A1222" t="n">
@@ -32366,7 +32384,9 @@
       <c r="F1222" t="n">
         <v>30620</v>
       </c>
-      <c r="G1222" t="inlineStr"/>
+      <c r="G1222" t="n">
+        <v>810.8108108108327</v>
+      </c>
     </row>
     <row r="1223">
       <c r="A1223" t="n">
@@ -32391,7 +32411,9 @@
       <c r="F1223" t="n">
         <v>32330</v>
       </c>
-      <c r="G1223" t="inlineStr"/>
+      <c r="G1223" t="n">
+        <v>260.8695652173936</v>
+      </c>
     </row>
     <row r="1224">
       <c r="A1224" t="n">
@@ -32416,7 +32438,9 @@
       <c r="F1224" t="n">
         <v>21756</v>
       </c>
-      <c r="G1224" t="inlineStr"/>
+      <c r="G1224" t="n">
+        <v>161.2903225806452</v>
+      </c>
     </row>
     <row r="1225">
       <c r="A1225" t="n">
@@ -32441,7 +32465,9 @@
       <c r="F1225" t="n">
         <v>14509</v>
       </c>
-      <c r="G1225" t="inlineStr"/>
+      <c r="G1225" t="n">
+        <v>112.5703564727959</v>
+      </c>
     </row>
     <row r="1226">
       <c r="A1226" t="n">
@@ -32466,7 +32492,9 @@
       <c r="F1226" t="n">
         <v>17786</v>
       </c>
-      <c r="G1226" t="inlineStr"/>
+      <c r="G1226" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="1227">
       <c r="A1227" t="n">
@@ -32491,7 +32519,9 @@
       <c r="F1227" t="n">
         <v>16757</v>
       </c>
-      <c r="G1227" t="inlineStr"/>
+      <c r="G1227" t="n">
+        <v>112.5703564727959</v>
+      </c>
     </row>
     <row r="1228">
       <c r="A1228" t="n">
@@ -32516,7 +32546,9 @@
       <c r="F1228" t="n">
         <v>22002</v>
       </c>
-      <c r="G1228" t="inlineStr"/>
+      <c r="G1228" t="n">
+        <v>119.2842942345929</v>
+      </c>
     </row>
     <row r="1229">
       <c r="A1229" t="n">
@@ -32541,7 +32573,9 @@
       <c r="F1229" t="n">
         <v>28270</v>
       </c>
-      <c r="G1229" t="inlineStr"/>
+      <c r="G1229" t="n">
+        <v>722.8915662650777</v>
+      </c>
     </row>
     <row r="1230">
       <c r="A1230" t="n">
@@ -32567,7 +32601,7 @@
         <v>22833</v>
       </c>
       <c r="G1230" t="n">
-        <v>350.8771929824561</v>
+        <v>78.53403141361278</v>
       </c>
     </row>
     <row r="1231">
@@ -32593,7 +32627,9 @@
       <c r="F1231" t="n">
         <v>26653</v>
       </c>
-      <c r="G1231" t="inlineStr"/>
+      <c r="G1231" t="n">
+        <v>129.8701298701299</v>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" t="n">
@@ -32618,7 +32654,9 @@
       <c r="F1232" t="n">
         <v>21883</v>
       </c>
-      <c r="G1232" t="inlineStr"/>
+      <c r="G1232" t="n">
+        <v>333.3333333333333</v>
+      </c>
     </row>
     <row r="1233">
       <c r="A1233" t="n">
@@ -32643,7 +32681,9 @@
       <c r="F1233" t="n">
         <v>25094</v>
       </c>
-      <c r="G1233" t="inlineStr"/>
+      <c r="G1233" t="n">
+        <v>324.3243243243278</v>
+      </c>
     </row>
     <row r="1234">
       <c r="A1234" t="n">
@@ -32668,7 +32708,9 @@
       <c r="F1234" t="n">
         <v>26657</v>
       </c>
-      <c r="G1234" t="inlineStr"/>
+      <c r="G1234" t="n">
+        <v>154.2416452442167</v>
+      </c>
     </row>
     <row r="1235">
       <c r="A1235" t="n">
@@ -32693,7 +32735,9 @@
       <c r="F1235" t="n">
         <v>31343</v>
       </c>
-      <c r="G1235" t="inlineStr"/>
+      <c r="G1235" t="n">
+        <v>160.8579088471867</v>
+      </c>
     </row>
     <row r="1236">
       <c r="A1236" t="n">
@@ -32718,7 +32762,9 @@
       <c r="F1236" t="n">
         <v>11451</v>
       </c>
-      <c r="G1236" t="inlineStr"/>
+      <c r="G1236" t="n">
+        <v>444.4444444444445</v>
+      </c>
     </row>
     <row r="1237">
       <c r="A1237" t="n">
@@ -32744,7 +32790,7 @@
         <v>29767</v>
       </c>
       <c r="G1237" t="n">
-        <v>72.8155339805827</v>
+        <v>18.08863430810974</v>
       </c>
     </row>
     <row r="1238">
@@ -32770,7 +32816,9 @@
       <c r="F1238" t="n">
         <v>24550</v>
       </c>
-      <c r="G1238" t="inlineStr"/>
+      <c r="G1238" t="n">
+        <v>110.0917431192665</v>
+      </c>
     </row>
     <row r="1239">
       <c r="A1239" t="n">
@@ -32795,7 +32843,9 @@
       <c r="F1239" t="n">
         <v>15330</v>
       </c>
-      <c r="G1239" t="inlineStr"/>
+      <c r="G1239" t="n">
+        <v>714.2857142857143</v>
+      </c>
     </row>
     <row r="1240">
       <c r="A1240" t="n">
@@ -32820,7 +32870,9 @@
       <c r="F1240" t="n">
         <v>12808</v>
       </c>
-      <c r="G1240" t="inlineStr"/>
+      <c r="G1240" t="n">
+        <v>153.8461538461538</v>
+      </c>
     </row>
     <row r="1241">
       <c r="A1241" t="n">
@@ -32845,7 +32897,9 @@
       <c r="F1241" t="n">
         <v>13965</v>
       </c>
-      <c r="G1241" t="inlineStr"/>
+      <c r="G1241" t="n">
+        <v>166.2049861495863</v>
+      </c>
     </row>
     <row r="1242">
       <c r="A1242" t="n">
@@ -32870,7 +32924,9 @@
       <c r="F1242" t="n">
         <v>9166</v>
       </c>
-      <c r="G1242" t="inlineStr"/>
+      <c r="G1242" t="n">
+        <v>59999.99999999987</v>
+      </c>
     </row>
     <row r="1243">
       <c r="A1243" t="n">
@@ -32896,7 +32952,7 @@
         <v>24342</v>
       </c>
       <c r="G1243" t="n">
-        <v>207.6124567474077</v>
+        <v>78.94736842105243</v>
       </c>
     </row>
     <row r="1244">
@@ -32922,7 +32978,9 @@
       <c r="F1244" t="n">
         <v>14140</v>
       </c>
-      <c r="G1244" t="inlineStr"/>
+      <c r="G1244" t="n">
+        <v>810.8108108108327</v>
+      </c>
     </row>
     <row r="1245">
       <c r="A1245" t="n">
@@ -32947,7 +33005,9 @@
       <c r="F1245" t="n">
         <v>28469</v>
       </c>
-      <c r="G1245" t="inlineStr"/>
+      <c r="G1245" t="n">
+        <v>631.5789473684343</v>
+      </c>
     </row>
     <row r="1246">
       <c r="A1246" t="n">
@@ -32972,7 +33032,9 @@
       <c r="F1246" t="n">
         <v>20954</v>
       </c>
-      <c r="G1246" t="inlineStr"/>
+      <c r="G1246" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="1247">
       <c r="A1247" t="n">
@@ -32997,7 +33059,9 @@
       <c r="F1247" t="n">
         <v>25157</v>
       </c>
-      <c r="G1247" t="inlineStr"/>
+      <c r="G1247" t="n">
+        <v>184.0490797546024</v>
+      </c>
     </row>
     <row r="1248">
       <c r="A1248" t="n">
@@ -33023,7 +33087,7 @@
         <v>23504</v>
       </c>
       <c r="G1248" t="n">
-        <v>243.9024390243902</v>
+        <v>54.05405405405406</v>
       </c>
     </row>
     <row r="1249">
@@ -33049,7 +33113,9 @@
       <c r="F1249" t="n">
         <v>5768</v>
       </c>
-      <c r="G1249" t="inlineStr"/>
+      <c r="G1249" t="n">
+        <v>833.3333333333334</v>
+      </c>
     </row>
     <row r="1250">
       <c r="A1250" t="n">
@@ -33074,7 +33140,9 @@
       <c r="F1250" t="n">
         <v>23602</v>
       </c>
-      <c r="G1250" t="inlineStr"/>
+      <c r="G1250" t="n">
+        <v>25.74002574002574</v>
+      </c>
     </row>
     <row r="1251">
       <c r="A1251" t="n">
@@ -33099,7 +33167,9 @@
       <c r="F1251" t="n">
         <v>23838</v>
       </c>
-      <c r="G1251" t="inlineStr"/>
+      <c r="G1251" t="n">
+        <v>29.61500493583413</v>
+      </c>
     </row>
     <row r="1252">
       <c r="A1252" t="n">
@@ -33125,7 +33195,7 @@
         <v>17538</v>
       </c>
       <c r="G1252" t="n">
-        <v>212.0141342756214</v>
+        <v>82.87292817679536</v>
       </c>
     </row>
     <row r="1253">
@@ -33151,7 +33221,9 @@
       <c r="F1253" t="n">
         <v>11276</v>
       </c>
-      <c r="G1253" t="inlineStr"/>
+      <c r="G1253" t="n">
+        <v>147.0588235294118</v>
+      </c>
     </row>
     <row r="1254">
       <c r="A1254" t="n">
@@ -33176,7 +33248,9 @@
       <c r="F1254" t="n">
         <v>15470</v>
       </c>
-      <c r="G1254" t="inlineStr"/>
+      <c r="G1254" t="n">
+        <v>149.2537313432836</v>
+      </c>
     </row>
     <row r="1255">
       <c r="A1255" t="n">
@@ -33201,7 +33275,9 @@
       <c r="F1255" t="n">
         <v>16333</v>
       </c>
-      <c r="G1255" t="inlineStr"/>
+      <c r="G1255" t="n">
+        <v>224.7191011235955</v>
+      </c>
     </row>
     <row r="1256">
       <c r="A1256" t="n">
@@ -33226,7 +33302,9 @@
       <c r="F1256" t="n">
         <v>15556</v>
       </c>
-      <c r="G1256" t="inlineStr"/>
+      <c r="G1256" t="n">
+        <v>82.98755186721992</v>
+      </c>
     </row>
     <row r="1257">
       <c r="A1257" t="n">
@@ -33251,7 +33329,9 @@
       <c r="F1257" t="n">
         <v>16394</v>
       </c>
-      <c r="G1257" t="inlineStr"/>
+      <c r="G1257" t="n">
+        <v>89.95502248875535</v>
+      </c>
     </row>
     <row r="1258">
       <c r="A1258" t="n">
@@ -33276,7 +33356,9 @@
       <c r="F1258" t="n">
         <v>19729</v>
       </c>
-      <c r="G1258" t="inlineStr"/>
+      <c r="G1258" t="n">
+        <v>189.274447949528</v>
+      </c>
     </row>
     <row r="1259">
       <c r="A1259" t="n">
@@ -33301,7 +33383,9 @@
       <c r="F1259" t="n">
         <v>21889</v>
       </c>
-      <c r="G1259" t="inlineStr"/>
+      <c r="G1259" t="n">
+        <v>800</v>
+      </c>
     </row>
     <row r="1260">
       <c r="A1260" t="n">
@@ -33326,7 +33410,9 @@
       <c r="F1260" t="n">
         <v>32457</v>
       </c>
-      <c r="G1260" t="inlineStr"/>
+      <c r="G1260" t="n">
+        <v>62.82722513088992</v>
+      </c>
     </row>
     <row r="1261">
       <c r="A1261" t="n">
@@ -33351,7 +33437,9 @@
       <c r="F1261" t="n">
         <v>15004</v>
       </c>
-      <c r="G1261" t="inlineStr"/>
+      <c r="G1261" t="n">
+        <v>194.1747572815534</v>
+      </c>
     </row>
     <row r="1262">
       <c r="A1262" t="n">
@@ -33376,7 +33464,9 @@
       <c r="F1262" t="n">
         <v>21688</v>
       </c>
-      <c r="G1262" t="inlineStr"/>
+      <c r="G1262" t="n">
+        <v>120.0000000000005</v>
+      </c>
     </row>
     <row r="1263">
       <c r="A1263" t="n">
@@ -33402,7 +33492,7 @@
         <v>24766</v>
       </c>
       <c r="G1263" t="n">
-        <v>517.2413793103538</v>
+        <v>89.95502248875535</v>
       </c>
     </row>
     <row r="1264">
@@ -33428,7 +33518,9 @@
       <c r="F1264" t="n">
         <v>12423</v>
       </c>
-      <c r="G1264" t="inlineStr"/>
+      <c r="G1264" t="n">
+        <v>72.55139056831941</v>
+      </c>
     </row>
     <row r="1265">
       <c r="A1265" t="n">
@@ -33453,7 +33545,9 @@
       <c r="F1265" t="n">
         <v>13470</v>
       </c>
-      <c r="G1265" t="inlineStr"/>
+      <c r="G1265" t="n">
+        <v>526.3157894736842</v>
+      </c>
     </row>
     <row r="1266">
       <c r="A1266" t="n">
@@ -33478,7 +33572,9 @@
       <c r="F1266" t="n">
         <v>16243</v>
       </c>
-      <c r="G1266" t="inlineStr"/>
+      <c r="G1266" t="n">
+        <v>114.7227533460812</v>
+      </c>
     </row>
     <row r="1267">
       <c r="A1267" t="n">
@@ -33503,7 +33599,9 @@
       <c r="F1267" t="n">
         <v>6169</v>
       </c>
-      <c r="G1267" t="inlineStr"/>
+      <c r="G1267" t="n">
+        <v>232.5581395348837</v>
+      </c>
     </row>
     <row r="1268">
       <c r="A1268" t="n">
@@ -33528,7 +33626,9 @@
       <c r="F1268" t="n">
         <v>24343</v>
       </c>
-      <c r="G1268" t="inlineStr"/>
+      <c r="G1268" t="n">
+        <v>229.0076335877898</v>
+      </c>
     </row>
     <row r="1269">
       <c r="A1269" t="n">
@@ -33553,7 +33653,9 @@
       <c r="F1269" t="n">
         <v>21943</v>
       </c>
-      <c r="G1269" t="inlineStr"/>
+      <c r="G1269" t="n">
+        <v>530.9734513274431</v>
+      </c>
     </row>
     <row r="1270">
       <c r="A1270" t="n">
@@ -33578,7 +33680,9 @@
       <c r="F1270" t="n">
         <v>13497</v>
       </c>
-      <c r="G1270" t="inlineStr"/>
+      <c r="G1270" t="n">
+        <v>769.2307692307693</v>
+      </c>
     </row>
     <row r="1271">
       <c r="A1271" t="n">
@@ -33603,7 +33707,9 @@
       <c r="F1271" t="n">
         <v>15310</v>
       </c>
-      <c r="G1271" t="inlineStr"/>
+      <c r="G1271" t="n">
+        <v>71.34363852556463</v>
+      </c>
     </row>
     <row r="1272">
       <c r="A1272" t="n">
@@ -33628,7 +33734,9 @@
       <c r="F1272" t="n">
         <v>15980</v>
       </c>
-      <c r="G1272" t="inlineStr"/>
+      <c r="G1272" t="n">
+        <v>235.2941176470588</v>
+      </c>
     </row>
     <row r="1273">
       <c r="A1273" t="n">
@@ -33653,7 +33761,9 @@
       <c r="F1273" t="n">
         <v>17723</v>
       </c>
-      <c r="G1273" t="inlineStr"/>
+      <c r="G1273" t="n">
+        <v>576.923076923088</v>
+      </c>
     </row>
     <row r="1274">
       <c r="A1274" t="n">
@@ -33679,7 +33789,7 @@
         <v>13900</v>
       </c>
       <c r="G1274" t="n">
-        <v>103.4482758620697</v>
+        <v>23.31908278274389</v>
       </c>
     </row>
     <row r="1275">
@@ -33705,7 +33815,9 @@
       <c r="F1275" t="n">
         <v>14926</v>
       </c>
-      <c r="G1275" t="inlineStr"/>
+      <c r="G1275" t="n">
+        <v>705.8823529412097</v>
+      </c>
     </row>
     <row r="1276">
       <c r="A1276" t="n">
@@ -33731,7 +33843,7 @@
         <v>23505</v>
       </c>
       <c r="G1276" t="n">
-        <v>186.9158878504673</v>
+        <v>43.7636761487965</v>
       </c>
     </row>
     <row r="1277">
@@ -33757,7 +33869,9 @@
       <c r="F1277" t="n">
         <v>28159</v>
       </c>
-      <c r="G1277" t="inlineStr"/>
+      <c r="G1277" t="n">
+        <v>60.36217303822926</v>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="n">
@@ -33782,7 +33896,9 @@
       <c r="F1278" t="n">
         <v>17365</v>
       </c>
-      <c r="G1278" t="inlineStr"/>
+      <c r="G1278" t="n">
+        <v>35.90664272890485</v>
+      </c>
     </row>
     <row r="1279">
       <c r="A1279" t="n">
@@ -33807,7 +33923,9 @@
       <c r="F1279" t="n">
         <v>21944</v>
       </c>
-      <c r="G1279" t="inlineStr"/>
+      <c r="G1279" t="n">
+        <v>165.2892561983471</v>
+      </c>
     </row>
     <row r="1280">
       <c r="A1280" t="n">
@@ -33832,7 +33950,9 @@
       <c r="F1280" t="n">
         <v>29770</v>
       </c>
-      <c r="G1280" t="inlineStr"/>
+      <c r="G1280" t="n">
+        <v>239.0438247011971</v>
+      </c>
     </row>
     <row r="1281">
       <c r="A1281" t="n">
@@ -33857,7 +33977,9 @@
       <c r="F1281" t="n">
         <v>21074</v>
       </c>
-      <c r="G1281" t="inlineStr"/>
+      <c r="G1281" t="n">
+        <v>258.6206896551769</v>
+      </c>
     </row>
     <row r="1282">
       <c r="A1282" t="n">
@@ -33882,7 +34004,9 @@
       <c r="F1282" t="n">
         <v>23841</v>
       </c>
-      <c r="G1282" t="inlineStr"/>
+      <c r="G1282" t="n">
+        <v>51.45797598627797</v>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="n">
@@ -33907,7 +34031,9 @@
       <c r="F1283" t="n">
         <v>25475</v>
       </c>
-      <c r="G1283" t="inlineStr"/>
+      <c r="G1283" t="n">
+        <v>937.5000000000588</v>
+      </c>
     </row>
     <row r="1284">
       <c r="A1284" t="n">
@@ -33932,7 +34058,9 @@
       <c r="F1284" t="n">
         <v>13412</v>
       </c>
-      <c r="G1284" t="inlineStr"/>
+      <c r="G1284" t="n">
+        <v>67.87330316742097</v>
+      </c>
     </row>
     <row r="1285">
       <c r="A1285" t="n">
@@ -33957,7 +34085,9 @@
       <c r="F1285" t="n">
         <v>13764</v>
       </c>
-      <c r="G1285" t="inlineStr"/>
+      <c r="G1285" t="n">
+        <v>87.71929824561403</v>
+      </c>
     </row>
     <row r="1286">
       <c r="A1286" t="n">
@@ -33982,7 +34112,9 @@
       <c r="F1286" t="n">
         <v>19960</v>
       </c>
-      <c r="G1286" t="inlineStr"/>
+      <c r="G1286" t="n">
+        <v>329.6703296703333</v>
+      </c>
     </row>
     <row r="1287">
       <c r="A1287" t="n">
@@ -34007,7 +34139,9 @@
       <c r="F1287" t="n">
         <v>27164</v>
       </c>
-      <c r="G1287" t="inlineStr"/>
+      <c r="G1287" t="n">
+        <v>270.2702702702703</v>
+      </c>
     </row>
     <row r="1288">
       <c r="A1288" t="n">
@@ -34032,7 +34166,9 @@
       <c r="F1288" t="n">
         <v>10104</v>
       </c>
-      <c r="G1288" t="inlineStr"/>
+      <c r="G1288" t="n">
+        <v>109.6892138939679</v>
+      </c>
     </row>
     <row r="1289">
       <c r="A1289" t="n">
@@ -34057,7 +34193,9 @@
       <c r="F1289" t="n">
         <v>14704</v>
       </c>
-      <c r="G1289" t="inlineStr"/>
+      <c r="G1289" t="n">
+        <v>461.5384615384757</v>
+      </c>
     </row>
     <row r="1290">
       <c r="A1290" t="n">
@@ -34083,7 +34221,7 @@
         <v>18554</v>
       </c>
       <c r="G1290" t="n">
-        <v>416.6666666666667</v>
+        <v>84.74576271186442</v>
       </c>
     </row>
     <row r="1291">
@@ -34109,7 +34247,9 @@
       <c r="F1291" t="n">
         <v>19840</v>
       </c>
-      <c r="G1291" t="inlineStr"/>
+      <c r="G1291" t="n">
+        <v>167.1309192200566</v>
+      </c>
     </row>
     <row r="1292">
       <c r="A1292" t="n">
@@ -34134,7 +34274,9 @@
       <c r="F1292" t="n">
         <v>21407</v>
       </c>
-      <c r="G1292" t="inlineStr"/>
+      <c r="G1292" t="n">
+        <v>69.84866123399286</v>
+      </c>
     </row>
     <row r="1293">
       <c r="A1293" t="n">
@@ -34159,7 +34301,9 @@
       <c r="F1293" t="n">
         <v>19872</v>
       </c>
-      <c r="G1293" t="inlineStr"/>
+      <c r="G1293" t="n">
+        <v>272.7272727272777</v>
+      </c>
     </row>
     <row r="1294">
       <c r="A1294" t="n">
@@ -34184,7 +34328,9 @@
       <c r="F1294" t="n">
         <v>18424</v>
       </c>
-      <c r="G1294" t="inlineStr"/>
+      <c r="G1294" t="n">
+        <v>124.223602484472</v>
+      </c>
     </row>
     <row r="1295">
       <c r="A1295" t="n">
@@ -34209,7 +34355,9 @@
       <c r="F1295" t="n">
         <v>16591</v>
       </c>
-      <c r="G1295" t="inlineStr"/>
+      <c r="G1295" t="n">
+        <v>1034.482758620761</v>
+      </c>
     </row>
     <row r="1296">
       <c r="A1296" t="n">
@@ -34234,7 +34382,9 @@
       <c r="F1296" t="n">
         <v>16715</v>
       </c>
-      <c r="G1296" t="inlineStr"/>
+      <c r="G1296" t="n">
+        <v>220.5882352941193</v>
+      </c>
     </row>
     <row r="1297">
       <c r="A1297" t="n">
@@ -34259,7 +34409,9 @@
       <c r="F1297" t="n">
         <v>14792</v>
       </c>
-      <c r="G1297" t="inlineStr"/>
+      <c r="G1297" t="n">
+        <v>186.3354037267104</v>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="n">
@@ -34284,7 +34436,9 @@
       <c r="F1298" t="n">
         <v>27183</v>
       </c>
-      <c r="G1298" t="inlineStr"/>
+      <c r="G1298" t="n">
+        <v>188.6792452830189</v>
+      </c>
     </row>
     <row r="1299">
       <c r="A1299" t="n">
@@ -34309,7 +34463,9 @@
       <c r="F1299" t="n">
         <v>30814</v>
       </c>
-      <c r="G1299" t="inlineStr"/>
+      <c r="G1299" t="n">
+        <v>769.2307692307693</v>
+      </c>
     </row>
     <row r="1300">
       <c r="A1300" t="n">
@@ -34334,7 +34490,9 @@
       <c r="F1300" t="n">
         <v>19477</v>
       </c>
-      <c r="G1300" t="inlineStr"/>
+      <c r="G1300" t="n">
+        <v>508.4745762712037</v>
+      </c>
     </row>
     <row r="1301">
       <c r="A1301" t="n">
@@ -34360,7 +34518,7 @@
         <v>20722</v>
       </c>
       <c r="G1301" t="n">
-        <v>800</v>
+        <v>169.0140845070442</v>
       </c>
     </row>
     <row r="1302">
@@ -34386,7 +34544,9 @@
       <c r="F1302" t="n">
         <v>32055</v>
       </c>
-      <c r="G1302" t="inlineStr"/>
+      <c r="G1302" t="n">
+        <v>314.1361256544535</v>
+      </c>
     </row>
     <row r="1303">
       <c r="A1303" t="n">
@@ -34411,7 +34571,9 @@
       <c r="F1303" t="n">
         <v>11049</v>
       </c>
-      <c r="G1303" t="inlineStr"/>
+      <c r="G1303" t="n">
+        <v>206.1855670103093</v>
+      </c>
     </row>
     <row r="1304">
       <c r="A1304" t="n">
@@ -34436,7 +34598,9 @@
       <c r="F1304" t="n">
         <v>18474</v>
       </c>
-      <c r="G1304" t="inlineStr"/>
+      <c r="G1304" t="n">
+        <v>49.66887417218551</v>
+      </c>
     </row>
     <row r="1305">
       <c r="A1305" t="n">
@@ -34461,7 +34625,9 @@
       <c r="F1305" t="n">
         <v>18586</v>
       </c>
-      <c r="G1305" t="inlineStr"/>
+      <c r="G1305" t="n">
+        <v>75.09386733416751</v>
+      </c>
     </row>
     <row r="1306">
       <c r="A1306" t="n">
@@ -34486,7 +34652,9 @@
       <c r="F1306" t="n">
         <v>22985</v>
       </c>
-      <c r="G1306" t="inlineStr"/>
+      <c r="G1306" t="n">
+        <v>214.2857142857173</v>
+      </c>
     </row>
     <row r="1307">
       <c r="A1307" t="n">
@@ -34511,7 +34679,9 @@
       <c r="F1307" t="n">
         <v>8820</v>
       </c>
-      <c r="G1307" t="inlineStr"/>
+      <c r="G1307" t="n">
+        <v>631.5789473684343</v>
+      </c>
     </row>
     <row r="1308">
       <c r="A1308" t="n">
@@ -34536,7 +34706,9 @@
       <c r="F1308" t="n">
         <v>23048</v>
       </c>
-      <c r="G1308" t="inlineStr"/>
+      <c r="G1308" t="n">
+        <v>1395.348837209432</v>
+      </c>
     </row>
     <row r="1309">
       <c r="A1309" t="n">
@@ -34561,7 +34733,9 @@
       <c r="F1309" t="n">
         <v>8480</v>
       </c>
-      <c r="G1309" t="inlineStr"/>
+      <c r="G1309" t="n">
+        <v>1071.42857142861</v>
+      </c>
     </row>
     <row r="1310">
       <c r="A1310" t="n">
@@ -34586,7 +34760,9 @@
       <c r="F1310" t="n">
         <v>29279</v>
       </c>
-      <c r="G1310" t="inlineStr"/>
+      <c r="G1310" t="n">
+        <v>254.2372881355953</v>
+      </c>
     </row>
     <row r="1311">
       <c r="A1311" t="n">
@@ -34611,7 +34787,9 @@
       <c r="F1311" t="n">
         <v>13997</v>
       </c>
-      <c r="G1311" t="inlineStr"/>
+      <c r="G1311" t="n">
+        <v>298.5074626865672</v>
+      </c>
     </row>
     <row r="1312">
       <c r="A1312" t="n">
@@ -34636,7 +34814,9 @@
       <c r="F1312" t="n">
         <v>26850</v>
       </c>
-      <c r="G1312" t="inlineStr"/>
+      <c r="G1312" t="n">
+        <v>100.8403361344545</v>
+      </c>
     </row>
     <row r="1313">
       <c r="A1313" t="n">
@@ -34661,7 +34841,9 @@
       <c r="F1313" t="n">
         <v>27364</v>
       </c>
-      <c r="G1313" t="inlineStr"/>
+      <c r="G1313" t="n">
+        <v>47.1327572663</v>
+      </c>
     </row>
     <row r="1314">
       <c r="A1314" t="n">
@@ -34686,7 +34868,9 @@
       <c r="F1314" t="n">
         <v>26649</v>
       </c>
-      <c r="G1314" t="inlineStr"/>
+      <c r="G1314" t="n">
+        <v>33.91746749576036</v>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" t="n">
@@ -34711,7 +34895,9 @@
       <c r="F1315" t="n">
         <v>12425</v>
       </c>
-      <c r="G1315" t="inlineStr"/>
+      <c r="G1315" t="n">
+        <v>14999.99999999999</v>
+      </c>
     </row>
     <row r="1316">
       <c r="A1316" t="n">
@@ -34736,7 +34922,9 @@
       <c r="F1316" t="n">
         <v>17032</v>
       </c>
-      <c r="G1316" t="inlineStr"/>
+      <c r="G1316" t="n">
+        <v>659.3406593406883</v>
+      </c>
     </row>
     <row r="1317">
       <c r="A1317" t="n">
@@ -34762,7 +34950,7 @@
         <v>23816</v>
       </c>
       <c r="G1317" t="n">
-        <v>379.7468354430427</v>
+        <v>89.41877794336837</v>
       </c>
     </row>
     <row r="1318">
@@ -34788,7 +34976,9 @@
       <c r="F1318" t="n">
         <v>17550</v>
       </c>
-      <c r="G1318" t="inlineStr"/>
+      <c r="G1318" t="n">
+        <v>277.7777777777778</v>
+      </c>
     </row>
     <row r="1319">
       <c r="A1319" t="n">
@@ -34813,7 +35003,9 @@
       <c r="F1319" t="n">
         <v>25319</v>
       </c>
-      <c r="G1319" t="inlineStr"/>
+      <c r="G1319" t="n">
+        <v>273.972602739726</v>
+      </c>
     </row>
     <row r="1320">
       <c r="A1320" t="n">
@@ -34838,7 +35030,9 @@
       <c r="F1320" t="n">
         <v>15651</v>
       </c>
-      <c r="G1320" t="inlineStr"/>
+      <c r="G1320" t="n">
+        <v>106.951871657754</v>
+      </c>
     </row>
     <row r="1321">
       <c r="A1321" t="n">
@@ -34863,7 +35057,9 @@
       <c r="F1321" t="n">
         <v>24304</v>
       </c>
-      <c r="G1321" t="inlineStr"/>
+      <c r="G1321" t="n">
+        <v>206.1855670103093</v>
+      </c>
     </row>
     <row r="1322">
       <c r="A1322" t="n">
@@ -34888,7 +35084,9 @@
       <c r="F1322" t="n">
         <v>9171</v>
       </c>
-      <c r="G1322" t="inlineStr"/>
+      <c r="G1322" t="n">
+        <v>566.037735849078</v>
+      </c>
     </row>
     <row r="1323">
       <c r="A1323" t="n">
@@ -34913,7 +35111,9 @@
       <c r="F1323" t="n">
         <v>25003</v>
       </c>
-      <c r="G1323" t="inlineStr"/>
+      <c r="G1323" t="n">
+        <v>638.2978723404527</v>
+      </c>
     </row>
     <row r="1324">
       <c r="A1324" t="n">
@@ -34938,7 +35138,9 @@
       <c r="F1324" t="n">
         <v>20706</v>
       </c>
-      <c r="G1324" t="inlineStr"/>
+      <c r="G1324" t="n">
+        <v>105.0788091068309</v>
+      </c>
     </row>
     <row r="1325">
       <c r="A1325" t="n">
@@ -34963,7 +35165,9 @@
       <c r="F1325" t="n">
         <v>12426</v>
       </c>
-      <c r="G1325" t="inlineStr"/>
+      <c r="G1325" t="n">
+        <v>631.5789473684343</v>
+      </c>
     </row>
     <row r="1326">
       <c r="A1326" t="n">
@@ -34988,7 +35192,9 @@
       <c r="F1326" t="n">
         <v>25908</v>
       </c>
-      <c r="G1326" t="inlineStr"/>
+      <c r="G1326" t="n">
+        <v>121.7038539553762</v>
+      </c>
     </row>
     <row r="1327">
       <c r="A1327" t="n">
@@ -35013,7 +35219,9 @@
       <c r="F1327" t="n">
         <v>12920</v>
       </c>
-      <c r="G1327" t="inlineStr"/>
+      <c r="G1327" t="n">
+        <v>2142.857142857449</v>
+      </c>
     </row>
     <row r="1328">
       <c r="A1328" t="n">
@@ -35038,7 +35246,9 @@
       <c r="F1328" t="n">
         <v>22051</v>
       </c>
-      <c r="G1328" t="inlineStr"/>
+      <c r="G1328" t="n">
+        <v>1224.489795918467</v>
+      </c>
     </row>
     <row r="1329">
       <c r="A1329" t="n">
@@ -35063,7 +35273,9 @@
       <c r="F1329" t="n">
         <v>12577</v>
       </c>
-      <c r="G1329" t="inlineStr"/>
+      <c r="G1329" t="n">
+        <v>123.9669421487614</v>
+      </c>
     </row>
     <row r="1330">
       <c r="A1330" t="n">
@@ -35088,7 +35300,9 @@
       <c r="F1330" t="n">
         <v>25002</v>
       </c>
-      <c r="G1330" t="inlineStr"/>
+      <c r="G1330" t="n">
+        <v>135.4401805869081</v>
+      </c>
     </row>
     <row r="1331">
       <c r="A1331" t="n">
@@ -35113,7 +35327,9 @@
       <c r="F1331" t="n">
         <v>29925</v>
       </c>
-      <c r="G1331" t="inlineStr"/>
+      <c r="G1331" t="n">
+        <v>209.7902097902127</v>
+      </c>
     </row>
     <row r="1332">
       <c r="A1332" t="n">
@@ -35138,7 +35354,9 @@
       <c r="F1332" t="n">
         <v>23656</v>
       </c>
-      <c r="G1332" t="inlineStr"/>
+      <c r="G1332" t="n">
+        <v>310.8808290155505</v>
+      </c>
     </row>
     <row r="1333">
       <c r="A1333" t="n">
@@ -35164,7 +35382,7 @@
         <v>17881</v>
       </c>
       <c r="G1333" t="n">
-        <v>389.6103896103997</v>
+        <v>105.4481546572939</v>
       </c>
     </row>
     <row r="1334">
@@ -35190,7 +35408,9 @@
       <c r="F1334" t="n">
         <v>19428</v>
       </c>
-      <c r="G1334" t="inlineStr"/>
+      <c r="G1334" t="n">
+        <v>55.29953917050702</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Data/MST/Fields.xlsx
+++ b/Data/MST/Fields.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1334"/>
+  <dimension ref="A1:G1406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35412,6 +35412,1950 @@
         <v>55.29953917050702</v>
       </c>
     </row>
+    <row r="1335">
+      <c r="A1335" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1335" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Aberg, Ludvig</t>
+        </is>
+      </c>
+      <c r="F1335" t="n">
+        <v>23950</v>
+      </c>
+      <c r="G1335" t="n">
+        <v>77.92207792207812</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1336" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Bennett, Daniel</t>
+        </is>
+      </c>
+      <c r="F1336" t="n">
+        <v>30332</v>
+      </c>
+      <c r="G1336" t="n">
+        <v>59999.99999999987</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1337" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Berger, Daniel</t>
+        </is>
+      </c>
+      <c r="F1337" t="n">
+        <v>17606</v>
+      </c>
+      <c r="G1337" t="n">
+        <v>170.4545454545474</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1338" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Bhatia, Akshay</t>
+        </is>
+      </c>
+      <c r="F1338" t="n">
+        <v>26096</v>
+      </c>
+      <c r="G1338" t="n">
+        <v>103.8062283737028</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1339" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Bradley, Keegan</t>
+        </is>
+      </c>
+      <c r="F1339" t="n">
+        <v>13872</v>
+      </c>
+      <c r="G1339" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1340" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Bridgeman, Jacob</t>
+        </is>
+      </c>
+      <c r="F1340" t="n">
+        <v>29433</v>
+      </c>
+      <c r="G1340" t="n">
+        <v>81.41112618724581</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1341" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Burns, Sam</t>
+        </is>
+      </c>
+      <c r="F1341" t="n">
+        <v>19483</v>
+      </c>
+      <c r="G1341" t="n">
+        <v>77.51937984496124</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1342" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Campbell, Brian</t>
+        </is>
+      </c>
+      <c r="F1342" t="n">
+        <v>18628</v>
+      </c>
+      <c r="G1342" t="n">
+        <v>30000.00000000003</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1343" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>Cantlay, Patrick</t>
+        </is>
+      </c>
+      <c r="F1343" t="n">
+        <v>15466</v>
+      </c>
+      <c r="G1343" t="n">
+        <v>64.17112299465255</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1344" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Cauley, Bud</t>
+        </is>
+      </c>
+      <c r="F1344" t="n">
+        <v>14502</v>
+      </c>
+      <c r="G1344" t="n">
+        <v>517.2413793103538</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1345" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Conners, Corey</t>
+        </is>
+      </c>
+      <c r="F1345" t="n">
+        <v>17576</v>
+      </c>
+      <c r="G1345" t="n">
+        <v>116.7315175097286</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1346" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Coody, Pierceson</t>
+        </is>
+      </c>
+      <c r="F1346" t="n">
+        <v>28309</v>
+      </c>
+      <c r="G1346" t="n">
+        <v>68.8863375430538</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1347" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>Dahmen, Joel</t>
+        </is>
+      </c>
+      <c r="F1347" t="n">
+        <v>14509</v>
+      </c>
+      <c r="G1347" t="n">
+        <v>255.3191489361746</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1348" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Day, Jason</t>
+        </is>
+      </c>
+      <c r="F1348" t="n">
+        <v>9771</v>
+      </c>
+      <c r="G1348" t="n">
+        <v>116.5048543689325</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1349" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>Echavarria, Nico</t>
+        </is>
+      </c>
+      <c r="F1349" t="n">
+        <v>22833</v>
+      </c>
+      <c r="G1349" t="n">
+        <v>169.0140845070442</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1350" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>English, Harris</t>
+        </is>
+      </c>
+      <c r="F1350" t="n">
+        <v>14577</v>
+      </c>
+      <c r="G1350" t="n">
+        <v>47.69475357710645</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1351" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>Fitzpatrick, Matt</t>
+        </is>
+      </c>
+      <c r="F1351" t="n">
+        <v>17646</v>
+      </c>
+      <c r="G1351" t="n">
+        <v>26.7022696929239</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1352" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Fleetwood, Tommy</t>
+        </is>
+      </c>
+      <c r="F1352" t="n">
+        <v>12294</v>
+      </c>
+      <c r="G1352" t="n">
+        <v>23.32814930015551</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1353" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Fowler, Rickie</t>
+        </is>
+      </c>
+      <c r="F1353" t="n">
+        <v>12965</v>
+      </c>
+      <c r="G1353" t="n">
+        <v>62.43496357960445</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1354" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Fox, Ryan</t>
+        </is>
+      </c>
+      <c r="F1354" t="n">
+        <v>11889</v>
+      </c>
+      <c r="G1354" t="n">
+        <v>263.1578947368421</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1355" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>Gerard, Ryan</t>
+        </is>
+      </c>
+      <c r="F1355" t="n">
+        <v>29767</v>
+      </c>
+      <c r="G1355" t="n">
+        <v>58.30903790087464</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1356" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Glover, Lucas</t>
+        </is>
+      </c>
+      <c r="F1356" t="n">
+        <v>7399</v>
+      </c>
+      <c r="G1356" t="n">
+        <v>722.8915662650777</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1357" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Gotterup, Chris</t>
+        </is>
+      </c>
+      <c r="F1357" t="n">
+        <v>27774</v>
+      </c>
+      <c r="G1357" t="n">
+        <v>66.81514476614684</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1358" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Greyserman, Max</t>
+        </is>
+      </c>
+      <c r="F1358" t="n">
+        <v>23465</v>
+      </c>
+      <c r="G1358" t="n">
+        <v>196.078431372549</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1359" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Griffin, Ben</t>
+        </is>
+      </c>
+      <c r="F1359" t="n">
+        <v>24968</v>
+      </c>
+      <c r="G1359" t="n">
+        <v>75.37688442211036</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1360" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Hall, Harry</t>
+        </is>
+      </c>
+      <c r="F1360" t="n">
+        <v>27194</v>
+      </c>
+      <c r="G1360" t="n">
+        <v>212.7659574468085</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1361" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Harman, Brian</t>
+        </is>
+      </c>
+      <c r="F1361" t="n">
+        <v>8825</v>
+      </c>
+      <c r="G1361" t="n">
+        <v>419.5804195804255</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1362" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Henley, Russell</t>
+        </is>
+      </c>
+      <c r="F1362" t="n">
+        <v>14578</v>
+      </c>
+      <c r="G1362" t="n">
+        <v>51.85825410544521</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1363" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Hisatsune, Ryo</t>
+        </is>
+      </c>
+      <c r="F1363" t="n">
+        <v>22760</v>
+      </c>
+      <c r="G1363" t="n">
+        <v>216.606498194949</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1364" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Hoge, Tom</t>
+        </is>
+      </c>
+      <c r="F1364" t="n">
+        <v>15575</v>
+      </c>
+      <c r="G1364" t="n">
+        <v>769.2307692307693</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1365" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Hojgaard, Nicolai</t>
+        </is>
+      </c>
+      <c r="F1365" t="n">
+        <v>23602</v>
+      </c>
+      <c r="G1365" t="n">
+        <v>65.07592190889356</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1366" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Horschel, Billy</t>
+        </is>
+      </c>
+      <c r="F1366" t="n">
+        <v>11276</v>
+      </c>
+      <c r="G1366" t="n">
+        <v>740.7407407407406</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1367" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Hovland, Viktor</t>
+        </is>
+      </c>
+      <c r="F1367" t="n">
+        <v>18841</v>
+      </c>
+      <c r="G1367" t="n">
+        <v>70.09345794392507</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1368" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Im, Sungjae</t>
+        </is>
+      </c>
+      <c r="F1368" t="n">
+        <v>17488</v>
+      </c>
+      <c r="G1368" t="n">
+        <v>243.9024390243902</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1369" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Kim, Michael</t>
+        </is>
+      </c>
+      <c r="F1369" t="n">
+        <v>17543</v>
+      </c>
+      <c r="G1369" t="n">
+        <v>530.9734513274431</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1370" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Kim, Si Woo</t>
+        </is>
+      </c>
+      <c r="F1370" t="n">
+        <v>14609</v>
+      </c>
+      <c r="G1370" t="n">
+        <v>35.10825043885317</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1371" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Kirk, Chris</t>
+        </is>
+      </c>
+      <c r="F1371" t="n">
+        <v>12423</v>
+      </c>
+      <c r="G1371" t="n">
+        <v>264.3171806167424</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1372" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Kitayama, Kurt</t>
+        </is>
+      </c>
+      <c r="F1372" t="n">
+        <v>21891</v>
+      </c>
+      <c r="G1372" t="n">
+        <v>59.88023952095809</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1373" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Knapp, Jake</t>
+        </is>
+      </c>
+      <c r="F1373" t="n">
+        <v>19396</v>
+      </c>
+      <c r="G1373" t="n">
+        <v>54.89478499542533</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1374" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>Lee, Min Woo</t>
+        </is>
+      </c>
+      <c r="F1374" t="n">
+        <v>16841</v>
+      </c>
+      <c r="G1374" t="n">
+        <v>49.01960784313725</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1375" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Lowry, Shane</t>
+        </is>
+      </c>
+      <c r="F1375" t="n">
+        <v>13900</v>
+      </c>
+      <c r="G1375" t="n">
+        <v>65.71741511500534</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1376" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>MacIntyre, Robert</t>
+        </is>
+      </c>
+      <c r="F1376" t="n">
+        <v>23323</v>
+      </c>
+      <c r="G1376" t="n">
+        <v>63.89776357827476</v>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1377" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>Matsuyama, Hideki</t>
+        </is>
+      </c>
+      <c r="F1377" t="n">
+        <v>13562</v>
+      </c>
+      <c r="G1377" t="n">
+        <v>49.01960784313725</v>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1378" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>McCarthy, Denny</t>
+        </is>
+      </c>
+      <c r="F1378" t="n">
+        <v>19870</v>
+      </c>
+      <c r="G1378" t="n">
+        <v>389.6103896103997</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1379" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>McCarty, Matt</t>
+        </is>
+      </c>
+      <c r="F1379" t="n">
+        <v>28635</v>
+      </c>
+      <c r="G1379" t="n">
+        <v>198.0198019801981</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1380" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>McIlroy, Rory</t>
+        </is>
+      </c>
+      <c r="F1380" t="n">
+        <v>10091</v>
+      </c>
+      <c r="G1380" t="n">
+        <v>12.43008079552517</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1381" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>McNealy, Maverick</t>
+        </is>
+      </c>
+      <c r="F1381" t="n">
+        <v>18634</v>
+      </c>
+      <c r="G1381" t="n">
+        <v>66.15214994487306</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1382" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>Mitchell, Keith</t>
+        </is>
+      </c>
+      <c r="F1382" t="n">
+        <v>17365</v>
+      </c>
+      <c r="G1382" t="n">
+        <v>82.41758241758265</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1383" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Moore, Taylor</t>
+        </is>
+      </c>
+      <c r="F1383" t="n">
+        <v>21944</v>
+      </c>
+      <c r="G1383" t="n">
+        <v>322.5806451612903</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1384" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>Morikawa, Collin</t>
+        </is>
+      </c>
+      <c r="F1384" t="n">
+        <v>22085</v>
+      </c>
+      <c r="G1384" t="n">
+        <v>35.4819633353046</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1385" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>Noren, Alex</t>
+        </is>
+      </c>
+      <c r="F1385" t="n">
+        <v>10419</v>
+      </c>
+      <c r="G1385" t="n">
+        <v>122.6993865030675</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1386" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Novak, Andrew</t>
+        </is>
+      </c>
+      <c r="F1386" t="n">
+        <v>23475</v>
+      </c>
+      <c r="G1386" t="n">
+        <v>447.7611940298574</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1387" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Pendrith, Taylor</t>
+        </is>
+      </c>
+      <c r="F1387" t="n">
+        <v>17780</v>
+      </c>
+      <c r="G1387" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1388" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Poston, J.T.</t>
+        </is>
+      </c>
+      <c r="F1388" t="n">
+        <v>21554</v>
+      </c>
+      <c r="G1388" t="n">
+        <v>238.0952380952381</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1389" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>Potgieter, Aldrich</t>
+        </is>
+      </c>
+      <c r="F1389" t="n">
+        <v>27900</v>
+      </c>
+      <c r="G1389" t="n">
+        <v>441.1764705882483</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1390" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Putnam, Andrew</t>
+        </is>
+      </c>
+      <c r="F1390" t="n">
+        <v>14704</v>
+      </c>
+      <c r="G1390" t="n">
+        <v>1153.846153846243</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1391" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Rodgers, Patrick</t>
+        </is>
+      </c>
+      <c r="F1391" t="n">
+        <v>16283</v>
+      </c>
+      <c r="G1391" t="n">
+        <v>257.5107296137361</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1392" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Rose, Justin</t>
+        </is>
+      </c>
+      <c r="F1392" t="n">
+        <v>6093</v>
+      </c>
+      <c r="G1392" t="n">
+        <v>74.53416149068305</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1393" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>Schauffele, Xander</t>
+        </is>
+      </c>
+      <c r="F1393" t="n">
+        <v>19895</v>
+      </c>
+      <c r="G1393" t="n">
+        <v>30.3030303030303</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1394" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>Scheffler, Scottie</t>
+        </is>
+      </c>
+      <c r="F1394" t="n">
+        <v>18417</v>
+      </c>
+      <c r="G1394" t="n">
+        <v>5.840552905675059</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1395" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Scott, Adam</t>
+        </is>
+      </c>
+      <c r="F1395" t="n">
+        <v>6430</v>
+      </c>
+      <c r="G1395" t="n">
+        <v>73.71007371007353</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1396" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>Smotherman, Austin</t>
+        </is>
+      </c>
+      <c r="F1396" t="n">
+        <v>22985</v>
+      </c>
+      <c r="G1396" t="n">
+        <v>394.7368421052684</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1397" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Spaun, J.J.</t>
+        </is>
+      </c>
+      <c r="F1397" t="n">
+        <v>17536</v>
+      </c>
+      <c r="G1397" t="n">
+        <v>90.49773755656108</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1398" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>Spieth, Jordan</t>
+        </is>
+      </c>
+      <c r="F1398" t="n">
+        <v>14636</v>
+      </c>
+      <c r="G1398" t="n">
+        <v>126.8498942917553</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1399" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Stevens, Sam</t>
+        </is>
+      </c>
+      <c r="F1399" t="n">
+        <v>25569</v>
+      </c>
+      <c r="G1399" t="n">
+        <v>129.5896328293748</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1400" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>Straka, Sepp</t>
+        </is>
+      </c>
+      <c r="F1400" t="n">
+        <v>17511</v>
+      </c>
+      <c r="G1400" t="n">
+        <v>128.4796573875809</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1401" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Taylor, Nick</t>
+        </is>
+      </c>
+      <c r="F1401" t="n">
+        <v>13126</v>
+      </c>
+      <c r="G1401" t="n">
+        <v>134.8314606741585</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1402" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1402" t="inlineStr">
+        <is>
+          <t>Theegala, Sahith</t>
+        </is>
+      </c>
+      <c r="F1402" t="n">
+        <v>23014</v>
+      </c>
+      <c r="G1402" t="n">
+        <v>160.4278074866319</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1403" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1403" t="inlineStr">
+        <is>
+          <t>Thomas, Justin</t>
+        </is>
+      </c>
+      <c r="F1403" t="n">
+        <v>14139</v>
+      </c>
+      <c r="G1403" t="n">
+        <v>94.19152276295104</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1404" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1404" t="inlineStr">
+        <is>
+          <t>Thorbjornsen, Michael</t>
+        </is>
+      </c>
+      <c r="F1404" t="n">
+        <v>26649</v>
+      </c>
+      <c r="G1404" t="n">
+        <v>108.4990958408688</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1405" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1405" t="inlineStr">
+        <is>
+          <t>Vegas, Jhonattan</t>
+        </is>
+      </c>
+      <c r="F1405" t="n">
+        <v>13508</v>
+      </c>
+      <c r="G1405" t="n">
+        <v>2307.692307692485</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Arnold Palmer Invitational presented by Mastercard</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>9</v>
+      </c>
+      <c r="D1406" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="E1406" t="inlineStr">
+        <is>
+          <t>Young, Cameron</t>
+        </is>
+      </c>
+      <c r="F1406" t="n">
+        <v>26651</v>
+      </c>
+      <c r="G1406" t="n">
+        <v>47.46835443037968</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
